--- a/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
+++ b/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
@@ -500,16 +500,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>25.96</x:v>
+        <x:v>29.1</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>-20.79</x:v>
+        <x:v>-18.81</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F2" s="0">
         <x:v>1.59</x:v>
@@ -520,16 +520,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>32.03</x:v>
+        <x:v>33.38</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>-14.57</x:v>
+        <x:v>-13.41</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F3" s="0">
         <x:v>1.54</x:v>
@@ -540,19 +540,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>131.47</x:v>
+        <x:v>129.51</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>-2.75</x:v>
+        <x:v>-4.02</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2.38</x:v>
+        <x:v>2.39</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -560,19 +560,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>38.7</x:v>
+        <x:v>44.65</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>-1.99</x:v>
+        <x:v>-1.41</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1.42</x:v>
+        <x:v>1.47</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -580,16 +580,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>36.4</x:v>
+        <x:v>34.1</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>-2.2</x:v>
+        <x:v>-3.85</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F6" s="0">
         <x:v>1.4</x:v>
@@ -600,16 +600,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>24.26</x:v>
+        <x:v>25.68</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>-19.87</x:v>
+        <x:v>-18.95</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>1.55</x:v>
@@ -620,16 +620,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>15.72</x:v>
+        <x:v>16.81</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>-14.96</x:v>
+        <x:v>-14.17</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>1.36</x:v>
@@ -640,16 +640,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>67.42</x:v>
+        <x:v>70.71</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>-14.74</x:v>
+        <x:v>-13.06</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>1.96</x:v>
@@ -660,16 +660,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>22.17</x:v>
+        <x:v>21.66</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>-16.34</x:v>
+        <x:v>-16.69</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F10" s="0">
         <x:v>1.46</x:v>
@@ -680,16 +680,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>27.78</x:v>
+        <x:v>29.16</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>-7.58</x:v>
+        <x:v>-6.58</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F11" s="0">
         <x:v>1.38</x:v>
@@ -700,16 +700,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>46.15</x:v>
+        <x:v>43.32</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>-8</x:v>
+        <x:v>-9.79</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F12" s="0">
         <x:v>1.59</x:v>
@@ -720,16 +720,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>27.94</x:v>
+        <x:v>29.54</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>-8.23</x:v>
+        <x:v>-7.09</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F13" s="0">
         <x:v>1.39</x:v>
@@ -740,19 +740,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>37.63</x:v>
+        <x:v>36.76</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>-0.63</x:v>
+        <x:v>-1.87</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1.38</x:v>
+        <x:v>1.39</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -760,16 +760,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>29.67</x:v>
+        <x:v>31.51</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>-12.44</x:v>
+        <x:v>-11.2</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F15" s="0">
         <x:v>1.48</x:v>
@@ -780,13 +780,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>22.07</x:v>
+        <x:v>27.7</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>-19.5</x:v>
+        <x:v>-15.79</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>100</x:v>
@@ -800,16 +800,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>34.38</x:v>
+        <x:v>35.28</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>-6.17</x:v>
+        <x:v>-5.54</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F17" s="0">
         <x:v>1.43</x:v>
@@ -820,16 +820,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>26.4</x:v>
+        <x:v>27.06</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>-10.72</x:v>
+        <x:v>-10.26</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F18" s="0">
         <x:v>1.42</x:v>
@@ -840,16 +840,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>20.55</x:v>
+        <x:v>23.31</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>-10.14</x:v>
+        <x:v>-8.09</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F19" s="0">
         <x:v>1.34</x:v>
@@ -860,16 +860,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>34.68</x:v>
+        <x:v>41.44</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>-13.22</x:v>
+        <x:v>-8.86</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>1.55</x:v>
@@ -880,19 +880,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>50.67</x:v>
+        <x:v>52.67</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>-1.22</x:v>
+        <x:v>-1.65</x:v>
       </x:c>
       <x:c r="E21" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1.52</x:v>
+        <x:v>1.55</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -900,16 +900,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>17.98</x:v>
+        <x:v>16.8</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>-14.47</x:v>
+        <x:v>-15.33</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>1.38</x:v>
@@ -920,19 +920,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>46.61</x:v>
+        <x:v>48.18</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>-1</x:v>
+        <x:v>-1.31</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1.48</x:v>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -940,16 +940,16 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>31.74</x:v>
+        <x:v>31.67</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>-20.39</x:v>
+        <x:v>-20.44</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F24" s="0">
         <x:v>1.66</x:v>
@@ -960,19 +960,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>25.86</x:v>
+        <x:v>25.57</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>-10.98</x:v>
+        <x:v>-10.5</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1.41</x:v>
+        <x:v>1.4</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -980,16 +980,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>13.06</x:v>
+        <x:v>13.69</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>-17.58</x:v>
+        <x:v>-17.12</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1.37</x:v>
@@ -1000,16 +1000,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>11.35</x:v>
+        <x:v>12.2</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>-22.57</x:v>
+        <x:v>-21.98</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>1.44</x:v>
@@ -1020,16 +1020,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>9.8</x:v>
+        <x:v>11.84</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>-18.75</x:v>
+        <x:v>-17.25</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>1.35</x:v>
@@ -1040,16 +1040,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>119.87</x:v>
+        <x:v>124.83</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>-7.65</x:v>
+        <x:v>-5.56</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F29" s="0">
         <x:v>2.38</x:v>
@@ -1060,19 +1060,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>302.91</x:v>
+        <x:v>310.28</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>-3.17</x:v>
+        <x:v>-3.86</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4.16</x:v>
+        <x:v>4.27</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -1080,16 +1080,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>28.02</x:v>
+        <x:v>33.94</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>-31.75</x:v>
+        <x:v>-28.59</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F31" s="0">
         <x:v>1.88</x:v>

--- a/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
+++ b/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
@@ -500,19 +500,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>29.1</x:v>
+        <x:v>24.31</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>-18.81</x:v>
+        <x:v>-19.16</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>1.59</x:v>
+        <x:v>1.54</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -520,19 +520,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>33.38</x:v>
+        <x:v>32.84</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>-13.41</x:v>
+        <x:v>-12.91</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1.54</x:v>
+        <x:v>1.52</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -540,16 +540,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>129.51</x:v>
+        <x:v>132.3</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>-4.02</x:v>
+        <x:v>-2.86</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F4" s="0">
         <x:v>2.39</x:v>
@@ -560,16 +560,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>44.65</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>-1.41</x:v>
+        <x:v>-3.52</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>1.47</x:v>
@@ -580,16 +580,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>34.1</x:v>
+        <x:v>34.87</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>-3.85</x:v>
+        <x:v>-3.3</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F6" s="0">
         <x:v>1.4</x:v>
@@ -600,16 +600,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>25.68</x:v>
+        <x:v>26.51</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>-18.95</x:v>
+        <x:v>-18.42</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>1.55</x:v>
@@ -620,16 +620,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>16.81</x:v>
+        <x:v>15.8</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>-14.17</x:v>
+        <x:v>-14.9</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>1.36</x:v>
@@ -640,16 +640,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>70.71</x:v>
+        <x:v>83.54</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>-13.06</x:v>
+        <x:v>-6.53</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>1.96</x:v>
@@ -660,7 +660,7 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>21.66</x:v>
+        <x:v>20.22</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>100</x:v>
@@ -669,10 +669,10 @@
         <x:v>-16.69</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1.46</x:v>
+        <x:v>1.44</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -680,16 +680,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>29.16</x:v>
+        <x:v>30.1</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>-6.58</x:v>
+        <x:v>-5.91</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F11" s="0">
         <x:v>1.38</x:v>
@@ -700,16 +700,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>43.32</x:v>
+        <x:v>47.61</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>-9.79</x:v>
+        <x:v>-7.08</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F12" s="0">
         <x:v>1.59</x:v>
@@ -720,16 +720,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>29.54</x:v>
+        <x:v>31.04</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>-7.09</x:v>
+        <x:v>-6.01</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F13" s="0">
         <x:v>1.39</x:v>
@@ -740,16 +740,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>36.76</x:v>
+        <x:v>36.39</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>-1.87</x:v>
+        <x:v>-2.13</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F14" s="0">
         <x:v>1.39</x:v>
@@ -760,19 +760,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>31.51</x:v>
+        <x:v>30.38</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>-11.2</x:v>
+        <x:v>-11.12</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1.48</x:v>
+        <x:v>1.47</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
@@ -780,13 +780,13 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>27.7</x:v>
+        <x:v>40.38</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>-15.79</x:v>
+        <x:v>-7.43</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>100</x:v>
@@ -800,16 +800,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>35.28</x:v>
+        <x:v>35.22</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>-5.54</x:v>
+        <x:v>-5.26</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F17" s="0">
         <x:v>1.43</x:v>
@@ -820,16 +820,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>27.06</x:v>
+        <x:v>27.93</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>-10.26</x:v>
+        <x:v>-9.64</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F18" s="0">
         <x:v>1.42</x:v>
@@ -840,16 +840,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>23.31</x:v>
+        <x:v>21.5</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>-8.09</x:v>
+        <x:v>-9.43</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F19" s="0">
         <x:v>1.34</x:v>
@@ -860,16 +860,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>41.44</x:v>
+        <x:v>41.92</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>-8.86</x:v>
+        <x:v>-8.55</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>1.55</x:v>
@@ -880,19 +880,19 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>52.67</x:v>
+        <x:v>49.1</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>-1.65</x:v>
+        <x:v>-4.13</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F21" s="0">
-        <x:v>1.55</x:v>
+        <x:v>1.56</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:6">
@@ -900,16 +900,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>16.8</x:v>
+        <x:v>16.49</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>-15.33</x:v>
+        <x:v>-15.55</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>1.38</x:v>
@@ -920,19 +920,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>48.18</x:v>
+        <x:v>48.38</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>-1.31</x:v>
+        <x:v>-1.5</x:v>
       </x:c>
       <x:c r="E23" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1.5</x:v>
+        <x:v>1.51</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -940,19 +940,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>31.67</x:v>
+        <x:v>29.14</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>-20.44</x:v>
+        <x:v>-20.76</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1.66</x:v>
+        <x:v>1.63</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -960,19 +960,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>25.57</x:v>
+        <x:v>20.41</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>-10.5</x:v>
+        <x:v>-12.87</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1.4</x:v>
+        <x:v>1.38</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -980,16 +980,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>13.69</x:v>
+        <x:v>14.14</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>-17.12</x:v>
+        <x:v>-16.79</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1.37</x:v>
@@ -1000,16 +1000,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>12.2</x:v>
+        <x:v>12.41</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>-21.98</x:v>
+        <x:v>-21.83</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>1.44</x:v>
@@ -1020,16 +1020,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>11.84</x:v>
+        <x:v>12.55</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>-17.25</x:v>
+        <x:v>-16.72</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>1.35</x:v>
@@ -1040,16 +1040,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>124.83</x:v>
+        <x:v>115.23</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>-5.56</x:v>
+        <x:v>-9.6</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F29" s="0">
         <x:v>2.38</x:v>
@@ -1060,16 +1060,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>310.28</x:v>
+        <x:v>313.19</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>-3.86</x:v>
+        <x:v>-3.18</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F30" s="0">
         <x:v>4.27</x:v>
@@ -1080,16 +1080,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>33.94</x:v>
+        <x:v>39.16</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>-28.59</x:v>
+        <x:v>-25.81</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F31" s="0">
         <x:v>1.88</x:v>

--- a/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
+++ b/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
@@ -500,19 +500,19 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>24.31</x:v>
+        <x:v>21.2</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>-19.16</x:v>
+        <x:v>-20.19</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F2" s="0">
-        <x:v>1.54</x:v>
+        <x:v>1.52</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:6">
@@ -520,19 +520,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>32.84</x:v>
+        <x:v>29.48</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>-12.91</x:v>
+        <x:v>-13.79</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1.52</x:v>
+        <x:v>1.5</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -540,16 +540,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>132.3</x:v>
+        <x:v>129.1</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>-2.86</x:v>
+        <x:v>-4.2</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F4" s="0">
         <x:v>2.39</x:v>
@@ -560,19 +560,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>42</x:v>
+        <x:v>40.08</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>-3.52</x:v>
+        <x:v>-3.89</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1.47</x:v>
+        <x:v>1.46</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -580,16 +580,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>34.87</x:v>
+        <x:v>31.71</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>-3.3</x:v>
+        <x:v>-5.56</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F6" s="0">
         <x:v>1.4</x:v>
@@ -600,19 +600,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>26.51</x:v>
+        <x:v>24.44</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>-18.42</x:v>
+        <x:v>-19.1</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1.55</x:v>
+        <x:v>1.54</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -620,16 +620,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>15.8</x:v>
+        <x:v>14.3</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>-14.9</x:v>
+        <x:v>-16.01</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>1.36</x:v>
@@ -640,16 +640,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>83.54</x:v>
+        <x:v>81.46</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>-6.53</x:v>
+        <x:v>-7.59</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>1.96</x:v>
@@ -660,19 +660,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>20.22</x:v>
+        <x:v>17.54</x:v>
       </x:c>
       <x:c r="C10" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>-16.69</x:v>
+        <x:v>-17.32</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1.44</x:v>
+        <x:v>1.42</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -680,16 +680,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>30.1</x:v>
+        <x:v>28.03</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>-5.91</x:v>
+        <x:v>-7.4</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F11" s="0">
         <x:v>1.38</x:v>
@@ -700,16 +700,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>47.61</x:v>
+        <x:v>44.62</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>-7.08</x:v>
+        <x:v>-8.97</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F12" s="0">
         <x:v>1.59</x:v>
@@ -720,16 +720,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>31.04</x:v>
+        <x:v>31.64</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>-6.01</x:v>
+        <x:v>-5.58</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F13" s="0">
         <x:v>1.39</x:v>
@@ -740,19 +740,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>36.39</x:v>
+        <x:v>40.61</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>-2.13</x:v>
+        <x:v>-0.96</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1.39</x:v>
+        <x:v>1.42</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -760,19 +760,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>30.38</x:v>
+        <x:v>25.59</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>-11.12</x:v>
+        <x:v>-12.09</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1.47</x:v>
+        <x:v>1.43</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
@@ -780,19 +780,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>40.38</x:v>
+        <x:v>43.66</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>-7.43</x:v>
+        <x:v>-2.24</x:v>
       </x:c>
       <x:c r="E16" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>1.52</x:v>
+        <x:v>1.47</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
@@ -800,19 +800,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>35.22</x:v>
+        <x:v>29.92</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>-5.26</x:v>
+        <x:v>-7.86</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>1.43</x:v>
+        <x:v>1.41</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
@@ -820,16 +820,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>27.93</x:v>
+        <x:v>28.15</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>-9.64</x:v>
+        <x:v>-9.49</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F18" s="0">
         <x:v>1.42</x:v>
@@ -840,16 +840,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>21.5</x:v>
+        <x:v>20.74</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>-9.43</x:v>
+        <x:v>-10</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F19" s="0">
         <x:v>1.34</x:v>
@@ -860,19 +860,19 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>41.92</x:v>
+        <x:v>36.09</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>-8.55</x:v>
+        <x:v>-11.84</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F20" s="0">
-        <x:v>1.55</x:v>
+        <x:v>1.54</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:6">
@@ -880,16 +880,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>49.1</x:v>
+        <x:v>52.96</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>-4.13</x:v>
+        <x:v>-1.65</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>1.56</x:v>
@@ -900,16 +900,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>16.49</x:v>
+        <x:v>16.18</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>23</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>-15.55</x:v>
+        <x:v>-15.78</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>1.38</x:v>
@@ -920,16 +920,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>48.38</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>-1.5</x:v>
+        <x:v>-2.61</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F23" s="0">
         <x:v>1.51</x:v>
@@ -940,19 +940,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>29.14</x:v>
+        <x:v>25.17</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>-20.76</x:v>
+        <x:v>-21.46</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1.63</x:v>
+        <x:v>1.59</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -960,16 +960,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>20.41</x:v>
+        <x:v>16.76</x:v>
       </x:c>
       <x:c r="C25" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>-12.87</x:v>
+        <x:v>-15.52</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>1.38</x:v>
@@ -980,16 +980,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>14.14</x:v>
+        <x:v>13.96</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>-16.79</x:v>
+        <x:v>-16.92</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1.37</x:v>
@@ -1000,16 +1000,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>12.41</x:v>
+        <x:v>11.14</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>-21.83</x:v>
+        <x:v>-22.71</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>1.44</x:v>
@@ -1020,16 +1020,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>12.55</x:v>
+        <x:v>11.18</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>-16.72</x:v>
+        <x:v>-17.74</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>1.35</x:v>
@@ -1040,16 +1040,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>115.23</x:v>
+        <x:v>111.92</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>-9.6</x:v>
+        <x:v>-10.99</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F29" s="0">
         <x:v>2.38</x:v>
@@ -1060,16 +1060,16 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>313.19</x:v>
+        <x:v>325.61</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>-3.18</x:v>
+        <x:v>-0.27</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F30" s="0">
         <x:v>4.27</x:v>
@@ -1080,16 +1080,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>39.16</x:v>
+        <x:v>34.82</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>-25.81</x:v>
+        <x:v>-28.12</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F31" s="0">
         <x:v>1.88</x:v>

--- a/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
+++ b/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
@@ -500,16 +500,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>21.2</x:v>
+        <x:v>26.68</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>-20.19</x:v>
+        <x:v>-16.58</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F2" s="0">
         <x:v>1.52</x:v>
@@ -520,19 +520,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>29.48</x:v>
+        <x:v>36.76</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>-13.79</x:v>
+        <x:v>-7.78</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1.5</x:v>
+        <x:v>1.48</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -540,19 +540,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>129.1</x:v>
+        <x:v>129.87</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>-4.2</x:v>
+        <x:v>-3.5</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2.39</x:v>
+        <x:v>2.38</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -560,16 +560,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>40.08</x:v>
+        <x:v>45.36</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>-3.89</x:v>
+        <x:v>-0.18</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>2</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>1.46</x:v>
@@ -580,16 +580,16 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>31.71</x:v>
+        <x:v>36.57</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>-5.56</x:v>
+        <x:v>-2.08</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F6" s="0">
         <x:v>1.4</x:v>
@@ -600,19 +600,19 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>24.44</x:v>
+        <x:v>28.1</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>-19.1</x:v>
+        <x:v>-16.51</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F7" s="0">
-        <x:v>1.54</x:v>
+        <x:v>1.53</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:6">
@@ -620,16 +620,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>14.3</x:v>
+        <x:v>22.15</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>-16.01</x:v>
+        <x:v>-10.24</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>1.36</x:v>
@@ -640,16 +640,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>81.46</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>-7.59</x:v>
+        <x:v>-4.77</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>1.96</x:v>
@@ -660,19 +660,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>17.54</x:v>
+        <x:v>22.04</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>100</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>-17.32</x:v>
+        <x:v>-13.48</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F10" s="0">
-        <x:v>1.42</x:v>
+        <x:v>1.41</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:6">
@@ -680,16 +680,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>28.03</x:v>
+        <x:v>32.6</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>-7.4</x:v>
+        <x:v>-4.1</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F11" s="0">
         <x:v>1.38</x:v>
@@ -700,16 +700,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>44.62</x:v>
+        <x:v>49.39</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>-8.97</x:v>
+        <x:v>-5.96</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F12" s="0">
         <x:v>1.59</x:v>
@@ -720,16 +720,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>31.64</x:v>
+        <x:v>34.33</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>-5.58</x:v>
+        <x:v>-3.65</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F13" s="0">
         <x:v>1.39</x:v>
@@ -740,16 +740,16 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>40.61</x:v>
+        <x:v>36.27</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>-0.96</x:v>
+        <x:v>-4.27</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="0">
         <x:v>1.42</x:v>
@@ -760,19 +760,19 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>25.59</x:v>
+        <x:v>32.25</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>-12.09</x:v>
+        <x:v>-7.14</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F15" s="0">
-        <x:v>1.43</x:v>
+        <x:v>1.42</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:6">
@@ -780,19 +780,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>43.66</x:v>
+        <x:v>47.42</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>-2.24</x:v>
+        <x:v>-5.14</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>100</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>1.47</x:v>
+        <x:v>1.55</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
@@ -800,19 +800,19 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>29.92</x:v>
+        <x:v>32.51</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>-7.86</x:v>
+        <x:v>-5.03</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F17" s="0">
-        <x:v>1.41</x:v>
+        <x:v>1.4</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6">
@@ -820,16 +820,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>28.15</x:v>
+        <x:v>31.58</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>-9.49</x:v>
+        <x:v>-7.02</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F18" s="0">
         <x:v>1.42</x:v>
@@ -840,16 +840,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>20.74</x:v>
+        <x:v>25.21</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>-10</x:v>
+        <x:v>-6.67</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F19" s="0">
         <x:v>1.34</x:v>
@@ -860,16 +860,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>36.09</x:v>
+        <x:v>39.04</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>-11.84</x:v>
+        <x:v>-9.93</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>1.54</x:v>
@@ -880,16 +880,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>52.96</x:v>
+        <x:v>44.39</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>-1.65</x:v>
+        <x:v>-7.16</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>1.56</x:v>
@@ -900,16 +900,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>16.18</x:v>
+        <x:v>21.82</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>-15.78</x:v>
+        <x:v>-11.68</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>1.38</x:v>
@@ -920,16 +920,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>47</x:v>
+        <x:v>50.74</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>-2.61</x:v>
+        <x:v>-0.13</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="F23" s="0">
         <x:v>1.51</x:v>
@@ -940,19 +940,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>25.17</x:v>
+        <x:v>28.73</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>-21.46</x:v>
+        <x:v>-17.79</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1.59</x:v>
+        <x:v>1.57</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -960,19 +960,19 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>16.76</x:v>
+        <x:v>18.85</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>100</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>-15.52</x:v>
+        <x:v>-13.28</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F25" s="0">
-        <x:v>1.38</x:v>
+        <x:v>1.37</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:6">
@@ -980,16 +980,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>13.96</x:v>
+        <x:v>18.59</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>-16.92</x:v>
+        <x:v>-13.55</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1.37</x:v>
@@ -1000,16 +1000,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>11.14</x:v>
+        <x:v>18.45</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>17</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>-22.71</x:v>
+        <x:v>-17.62</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>1.44</x:v>
@@ -1020,16 +1020,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>11.18</x:v>
+        <x:v>17.69</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>-17.74</x:v>
+        <x:v>-12.92</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>59</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>1.35</x:v>
@@ -1040,16 +1040,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>111.92</x:v>
+        <x:v>117.11</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>-10.99</x:v>
+        <x:v>-8.81</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F29" s="0">
         <x:v>2.38</x:v>
@@ -1060,19 +1060,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>325.61</x:v>
+        <x:v>341.51</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>-0.27</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E30" s="0">
-        <x:v>3</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4.27</x:v>
+        <x:v>4.42</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -1080,16 +1080,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>34.82</x:v>
+        <x:v>44.78</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>-28.12</x:v>
+        <x:v>-22.81</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="F31" s="0">
         <x:v>1.88</x:v>

--- a/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
+++ b/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
@@ -500,16 +500,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>26.68</x:v>
+        <x:v>24.92</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>-16.58</x:v>
+        <x:v>-17.74</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F2" s="0">
         <x:v>1.52</x:v>
@@ -520,19 +520,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>36.76</x:v>
+        <x:v>33.13</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>-7.78</x:v>
+        <x:v>-9.65</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1.48</x:v>
+        <x:v>1.47</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -540,19 +540,19 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>129.87</x:v>
+        <x:v>124.79</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>-3.5</x:v>
+        <x:v>-4.89</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>4</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F4" s="0">
-        <x:v>2.38</x:v>
+        <x:v>2.36</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:6">
@@ -560,19 +560,19 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>45.36</x:v>
+        <x:v>43.94</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>-0.18</x:v>
+        <x:v>-1.01</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F5" s="0">
-        <x:v>1.46</x:v>
+        <x:v>1.45</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:6">
@@ -580,19 +580,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>36.57</x:v>
+        <x:v>41.94</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>-2.08</x:v>
+        <x:v>-0.66</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>49</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1.4</x:v>
+        <x:v>1.43</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -600,16 +600,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>28.1</x:v>
+        <x:v>25.99</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>-16.51</x:v>
+        <x:v>-17.88</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>1.53</x:v>
@@ -620,16 +620,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>22.15</x:v>
+        <x:v>20.14</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>-10.24</x:v>
+        <x:v>-11.72</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>1.36</x:v>
@@ -640,16 +640,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>87</x:v>
+        <x:v>82.32</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>-4.77</x:v>
+        <x:v>-7.15</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>1.96</x:v>
@@ -660,16 +660,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>22.04</x:v>
+        <x:v>20.99</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>-13.48</x:v>
+        <x:v>-14.22</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F10" s="0">
         <x:v>1.41</x:v>
@@ -680,16 +680,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>32.6</x:v>
+        <x:v>30.22</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>-4.1</x:v>
+        <x:v>-5.82</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F11" s="0">
         <x:v>1.38</x:v>
@@ -700,16 +700,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>49.39</x:v>
+        <x:v>48.58</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>-5.96</x:v>
+        <x:v>-6.47</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>7</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F12" s="0">
         <x:v>1.59</x:v>
@@ -720,16 +720,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>34.33</x:v>
+        <x:v>31.74</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>-3.65</x:v>
+        <x:v>-5.51</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F13" s="0">
         <x:v>1.39</x:v>
@@ -740,19 +740,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>36.27</x:v>
+        <x:v>39.37</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>-4.27</x:v>
+        <x:v>-2.77</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>1</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1.42</x:v>
+        <x:v>1.43</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -760,16 +760,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>32.25</x:v>
+        <x:v>29.32</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>-7.14</x:v>
+        <x:v>-9.08</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F15" s="0">
         <x:v>1.42</x:v>
@@ -780,19 +780,19 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>47.42</x:v>
+        <x:v>44.6</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>-5.14</x:v>
+        <x:v>-7.23</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>0</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F16" s="0">
-        <x:v>1.55</x:v>
+        <x:v>1.56</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6">
@@ -800,16 +800,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>32.51</x:v>
+        <x:v>31.25</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>-5.03</x:v>
+        <x:v>-5.93</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F17" s="0">
         <x:v>1.4</x:v>
@@ -820,16 +820,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>31.58</x:v>
+        <x:v>28.52</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>-7.02</x:v>
+        <x:v>-9.18</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F18" s="0">
         <x:v>1.42</x:v>
@@ -840,16 +840,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>25.21</x:v>
+        <x:v>24.93</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>-6.67</x:v>
+        <x:v>-6.88</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F19" s="0">
         <x:v>1.34</x:v>
@@ -860,16 +860,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>39.04</x:v>
+        <x:v>37.74</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>-9.93</x:v>
+        <x:v>-10.7</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>1.54</x:v>
@@ -880,16 +880,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>44.39</x:v>
+        <x:v>45.54</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>-7.16</x:v>
+        <x:v>-6.42</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>3</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>1.56</x:v>
@@ -900,16 +900,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>21.82</x:v>
+        <x:v>20.02</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>-11.68</x:v>
+        <x:v>-12.99</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>49</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>1.38</x:v>
@@ -920,19 +920,19 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>50.74</x:v>
+        <x:v>48.97</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>-0.13</x:v>
+        <x:v>-1.88</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="F23" s="0">
-        <x:v>1.51</x:v>
+        <x:v>1.52</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:6">
@@ -940,19 +940,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>28.73</x:v>
+        <x:v>24.5</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>-17.79</x:v>
+        <x:v>-19.51</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1.57</x:v>
+        <x:v>1.55</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -960,16 +960,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>18.85</x:v>
+        <x:v>15.88</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>25</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>-13.28</x:v>
+        <x:v>-15.45</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>1.37</x:v>
@@ -980,16 +980,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>18.59</x:v>
+        <x:v>20.4</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>-13.55</x:v>
+        <x:v>-12.23</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1.37</x:v>
@@ -1000,16 +1000,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>18.45</x:v>
+        <x:v>15.7</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>18</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>-17.62</x:v>
+        <x:v>-19.54</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>1.44</x:v>
@@ -1020,16 +1020,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>17.69</x:v>
+        <x:v>15.66</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>-12.92</x:v>
+        <x:v>-14.42</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>60</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>1.35</x:v>
@@ -1040,16 +1040,16 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>117.11</x:v>
+        <x:v>127.04</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>-8.81</x:v>
+        <x:v>-4.64</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>9</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F29" s="0">
         <x:v>2.38</x:v>
@@ -1060,19 +1060,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>341.51</x:v>
+        <x:v>346.17</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>0</x:v>
+        <x:v>-0.9</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4.42</x:v>
+        <x:v>4.5</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -1080,16 +1080,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>44.78</x:v>
+        <x:v>41.85</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>-22.81</x:v>
+        <x:v>-24.38</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>46</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="F31" s="0">
         <x:v>1.88</x:v>

--- a/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
+++ b/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
@@ -500,16 +500,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>24.92</x:v>
+        <x:v>26.55</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>-17.74</x:v>
+        <x:v>-16.67</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F2" s="0">
         <x:v>1.52</x:v>
@@ -520,16 +520,16 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>33.13</x:v>
+        <x:v>31.24</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>-9.65</x:v>
+        <x:v>-10.87</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F3" s="0">
         <x:v>1.47</x:v>
@@ -540,16 +540,16 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="B4" s="0">
-        <x:v>124.79</x:v>
+        <x:v>118.46</x:v>
       </x:c>
       <x:c r="C4" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D4" s="0">
-        <x:v>-4.89</x:v>
+        <x:v>-7.58</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F4" s="0">
         <x:v>2.36</x:v>
@@ -560,16 +560,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>43.94</x:v>
+        <x:v>41.26</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>-1.01</x:v>
+        <x:v>-2.86</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>1.45</x:v>
@@ -580,19 +580,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>41.94</x:v>
+        <x:v>43.73</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>-0.66</x:v>
+        <x:v>-1.58</x:v>
       </x:c>
       <x:c r="E6" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1.43</x:v>
+        <x:v>1.46</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -600,16 +600,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>25.99</x:v>
+        <x:v>21.3</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>-17.88</x:v>
+        <x:v>-20.94</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>1.53</x:v>
@@ -620,16 +620,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>20.14</x:v>
+        <x:v>18.31</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>-11.72</x:v>
+        <x:v>-13.06</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>1.36</x:v>
@@ -640,16 +640,16 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>82.32</x:v>
+        <x:v>77.47</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>-7.15</x:v>
+        <x:v>-9.62</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F9" s="0">
         <x:v>1.96</x:v>
@@ -660,16 +660,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>20.99</x:v>
+        <x:v>19.54</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>-14.22</x:v>
+        <x:v>-15.25</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F10" s="0">
         <x:v>1.41</x:v>
@@ -680,16 +680,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>30.22</x:v>
+        <x:v>28.97</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>-5.82</x:v>
+        <x:v>-6.72</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F11" s="0">
         <x:v>1.38</x:v>
@@ -700,16 +700,16 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>48.58</x:v>
+        <x:v>46.15</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>-6.47</x:v>
+        <x:v>-8</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="F12" s="0">
         <x:v>1.59</x:v>
@@ -720,16 +720,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>31.74</x:v>
+        <x:v>32.34</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>-5.51</x:v>
+        <x:v>-5.08</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F13" s="0">
         <x:v>1.39</x:v>
@@ -740,19 +740,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>39.37</x:v>
+        <x:v>42.1</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>-2.77</x:v>
+        <x:v>-1.55</x:v>
       </x:c>
       <x:c r="E14" s="0">
-        <x:v>3</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1.43</x:v>
+        <x:v>1.44</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -760,16 +760,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>29.32</x:v>
+        <x:v>26.93</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>-9.08</x:v>
+        <x:v>-10.76</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F15" s="0">
         <x:v>1.42</x:v>
@@ -780,16 +780,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>44.6</x:v>
+        <x:v>42.25</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>-7.23</x:v>
+        <x:v>-8.74</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F16" s="0">
         <x:v>1.56</x:v>
@@ -800,16 +800,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>31.25</x:v>
+        <x:v>29.44</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>-5.93</x:v>
+        <x:v>-7.23</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F17" s="0">
         <x:v>1.4</x:v>
@@ -820,16 +820,16 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>28.52</x:v>
+        <x:v>25.9</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>-9.18</x:v>
+        <x:v>-11.03</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F18" s="0">
         <x:v>1.42</x:v>
@@ -840,16 +840,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>24.93</x:v>
+        <x:v>24.45</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>-6.88</x:v>
+        <x:v>-7.23</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F19" s="0">
         <x:v>1.34</x:v>
@@ -860,16 +860,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>37.74</x:v>
+        <x:v>36.33</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>-10.7</x:v>
+        <x:v>-11.61</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>1.54</x:v>
@@ -880,16 +880,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>45.54</x:v>
+        <x:v>44.68</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>-6.42</x:v>
+        <x:v>-6.97</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>1.56</x:v>
@@ -900,16 +900,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>20.02</x:v>
+        <x:v>19.47</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>-12.99</x:v>
+        <x:v>-13.39</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>1.38</x:v>
@@ -920,16 +920,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>48.97</x:v>
+        <x:v>48.28</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>-1.88</x:v>
+        <x:v>-2.34</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>3</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="F23" s="0">
         <x:v>1.52</x:v>
@@ -940,19 +940,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>24.5</x:v>
+        <x:v>19.32</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>-19.51</x:v>
+        <x:v>-21.69</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1.55</x:v>
+        <x:v>1.52</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -960,16 +960,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>15.88</x:v>
+        <x:v>16.25</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>-15.45</x:v>
+        <x:v>-15.18</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>1.37</x:v>
@@ -980,16 +980,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>20.4</x:v>
+        <x:v>18.04</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>-12.23</x:v>
+        <x:v>-13.95</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1.37</x:v>
@@ -1000,16 +1000,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>15.7</x:v>
+        <x:v>13.04</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>-19.54</x:v>
+        <x:v>-21.39</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>1.44</x:v>
@@ -1020,16 +1020,16 @@
         <x:v>32</x:v>
       </x:c>
       <x:c r="B28" s="0">
-        <x:v>15.66</x:v>
+        <x:v>13.69</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D28" s="0">
-        <x:v>-14.42</x:v>
+        <x:v>-15.88</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>1.35</x:v>
@@ -1040,19 +1040,19 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>127.04</x:v>
+        <x:v>136.76</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>-4.64</x:v>
+        <x:v>-1.24</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>12</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>2.38</x:v>
+        <x:v>2.4</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -1060,19 +1060,19 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>346.17</x:v>
+        <x:v>370.03</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D30" s="0">
-        <x:v>-0.9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E30" s="0">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4.5</x:v>
+        <x:v>4.7</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -1080,16 +1080,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>41.85</x:v>
+        <x:v>41.38</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>-24.38</x:v>
+        <x:v>-24.62</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="F31" s="0">
         <x:v>1.88</x:v>

--- a/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
+++ b/app/borsa/dip-zirve-analizi/data/dip-zirve.xlsx
@@ -500,16 +500,16 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="B2" s="0">
-        <x:v>26.55</x:v>
+        <x:v>25.24</x:v>
       </x:c>
       <x:c r="C2" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D2" s="0">
-        <x:v>-16.67</x:v>
+        <x:v>-17.53</x:v>
       </x:c>
       <x:c r="E2" s="0">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F2" s="0">
         <x:v>1.52</x:v>
@@ -520,19 +520,19 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B3" s="0">
-        <x:v>31.24</x:v>
+        <x:v>27.9</x:v>
       </x:c>
       <x:c r="C3" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D3" s="0">
-        <x:v>-10.87</x:v>
+        <x:v>-12.52</x:v>
       </x:c>
       <x:c r="E3" s="0">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F3" s="0">
-        <x:v>1.47</x:v>
+        <x:v>1.46</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:6">
@@ -549,7 +549,7 @@
         <x:v>-7.58</x:v>
       </x:c>
       <x:c r="E4" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="F4" s="0">
         <x:v>2.36</x:v>
@@ -560,16 +560,16 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="B5" s="0">
-        <x:v>41.26</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C5" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>-2.86</x:v>
+        <x:v>-1.66</x:v>
       </x:c>
       <x:c r="E5" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F5" s="0">
         <x:v>1.45</x:v>
@@ -580,19 +580,19 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B6" s="0">
-        <x:v>43.73</x:v>
+        <x:v>38.96</x:v>
       </x:c>
       <x:c r="C6" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D6" s="0">
-        <x:v>-1.58</x:v>
+        <x:v>-5.45</x:v>
       </x:c>
       <x:c r="E6" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F6" s="0">
-        <x:v>1.46</x:v>
+        <x:v>1.47</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:6">
@@ -600,16 +600,16 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="B7" s="0">
-        <x:v>21.3</x:v>
+        <x:v>19.89</x:v>
       </x:c>
       <x:c r="C7" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>-20.94</x:v>
+        <x:v>-21.85</x:v>
       </x:c>
       <x:c r="E7" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F7" s="0">
         <x:v>1.53</x:v>
@@ -620,16 +620,16 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="0">
-        <x:v>18.31</x:v>
+        <x:v>16.31</x:v>
       </x:c>
       <x:c r="C8" s="0">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D8" s="0">
-        <x:v>-13.06</x:v>
+        <x:v>-14.54</x:v>
       </x:c>
       <x:c r="E8" s="0">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F8" s="0">
         <x:v>1.36</x:v>
@@ -640,19 +640,19 @@
         <x:v>13</x:v>
       </x:c>
       <x:c r="B9" s="0">
-        <x:v>77.47</x:v>
+        <x:v>70.89</x:v>
       </x:c>
       <x:c r="C9" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>-9.62</x:v>
+        <x:v>-8.83</x:v>
       </x:c>
       <x:c r="E9" s="0">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="F9" s="0">
-        <x:v>1.96</x:v>
+        <x:v>1.87</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:6">
@@ -660,16 +660,16 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="0">
-        <x:v>19.54</x:v>
+        <x:v>19.46</x:v>
       </x:c>
       <x:c r="C10" s="0">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D10" s="0">
-        <x:v>-15.25</x:v>
+        <x:v>-15.31</x:v>
       </x:c>
       <x:c r="E10" s="0">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="F10" s="0">
         <x:v>1.41</x:v>
@@ -680,16 +680,16 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B11" s="0">
-        <x:v>28.97</x:v>
+        <x:v>28.28</x:v>
       </x:c>
       <x:c r="C11" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>-6.72</x:v>
+        <x:v>-7.22</x:v>
       </x:c>
       <x:c r="E11" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F11" s="0">
         <x:v>1.38</x:v>
@@ -700,19 +700,19 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="B12" s="0">
-        <x:v>46.15</x:v>
+        <x:v>44.64</x:v>
       </x:c>
       <x:c r="C12" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D12" s="0">
-        <x:v>-8</x:v>
+        <x:v>-7.85</x:v>
       </x:c>
       <x:c r="E12" s="0">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="F12" s="0">
-        <x:v>1.59</x:v>
+        <x:v>1.57</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:6">
@@ -720,16 +720,16 @@
         <x:v>17</x:v>
       </x:c>
       <x:c r="B13" s="0">
-        <x:v>32.34</x:v>
+        <x:v>31.24</x:v>
       </x:c>
       <x:c r="C13" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D13" s="0">
-        <x:v>-5.08</x:v>
+        <x:v>-5.87</x:v>
       </x:c>
       <x:c r="E13" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F13" s="0">
         <x:v>1.39</x:v>
@@ -740,19 +740,19 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="B14" s="0">
-        <x:v>42.1</x:v>
+        <x:v>42.59</x:v>
       </x:c>
       <x:c r="C14" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D14" s="0">
-        <x:v>-1.55</x:v>
+        <x:v>-2.54</x:v>
       </x:c>
       <x:c r="E14" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="F14" s="0">
-        <x:v>1.44</x:v>
+        <x:v>1.46</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:6">
@@ -760,16 +760,16 @@
         <x:v>19</x:v>
       </x:c>
       <x:c r="B15" s="0">
-        <x:v>26.93</x:v>
+        <x:v>24.29</x:v>
       </x:c>
       <x:c r="C15" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>-10.76</x:v>
+        <x:v>-12.62</x:v>
       </x:c>
       <x:c r="E15" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F15" s="0">
         <x:v>1.42</x:v>
@@ -780,16 +780,16 @@
         <x:v>20</x:v>
       </x:c>
       <x:c r="B16" s="0">
-        <x:v>42.25</x:v>
+        <x:v>39.44</x:v>
       </x:c>
       <x:c r="C16" s="0">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D16" s="0">
-        <x:v>-8.74</x:v>
+        <x:v>-10.54</x:v>
       </x:c>
       <x:c r="E16" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F16" s="0">
         <x:v>1.56</x:v>
@@ -800,16 +800,16 @@
         <x:v>21</x:v>
       </x:c>
       <x:c r="B17" s="0">
-        <x:v>29.44</x:v>
+        <x:v>29.93</x:v>
       </x:c>
       <x:c r="C17" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>-7.23</x:v>
+        <x:v>-6.88</x:v>
       </x:c>
       <x:c r="E17" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F17" s="0">
         <x:v>1.4</x:v>
@@ -820,19 +820,19 @@
         <x:v>22</x:v>
       </x:c>
       <x:c r="B18" s="0">
-        <x:v>25.9</x:v>
+        <x:v>24.52</x:v>
       </x:c>
       <x:c r="C18" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D18" s="0">
-        <x:v>-11.03</x:v>
+        <x:v>-11.96</x:v>
       </x:c>
       <x:c r="E18" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F18" s="0">
-        <x:v>1.42</x:v>
+        <x:v>1.41</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6">
@@ -840,16 +840,16 @@
         <x:v>23</x:v>
       </x:c>
       <x:c r="B19" s="0">
-        <x:v>24.45</x:v>
+        <x:v>23.12</x:v>
       </x:c>
       <x:c r="C19" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D19" s="0">
-        <x:v>-7.23</x:v>
+        <x:v>-8.23</x:v>
       </x:c>
       <x:c r="E19" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F19" s="0">
         <x:v>1.34</x:v>
@@ -860,16 +860,16 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="B20" s="0">
-        <x:v>36.33</x:v>
+        <x:v>38.21</x:v>
       </x:c>
       <x:c r="C20" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D20" s="0">
-        <x:v>-11.61</x:v>
+        <x:v>-10.39</x:v>
       </x:c>
       <x:c r="E20" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F20" s="0">
         <x:v>1.54</x:v>
@@ -880,16 +880,16 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="B21" s="0">
-        <x:v>44.68</x:v>
+        <x:v>50.1</x:v>
       </x:c>
       <x:c r="C21" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D21" s="0">
-        <x:v>-6.97</x:v>
+        <x:v>-3.49</x:v>
       </x:c>
       <x:c r="E21" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="F21" s="0">
         <x:v>1.56</x:v>
@@ -900,16 +900,16 @@
         <x:v>26</x:v>
       </x:c>
       <x:c r="B22" s="0">
-        <x:v>19.47</x:v>
+        <x:v>17.61</x:v>
       </x:c>
       <x:c r="C22" s="0">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D22" s="0">
-        <x:v>-13.39</x:v>
+        <x:v>-14.74</x:v>
       </x:c>
       <x:c r="E22" s="0">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F22" s="0">
         <x:v>1.38</x:v>
@@ -920,16 +920,16 @@
         <x:v>27</x:v>
       </x:c>
       <x:c r="B23" s="0">
-        <x:v>48.28</x:v>
+        <x:v>50.35</x:v>
       </x:c>
       <x:c r="C23" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D23" s="0">
-        <x:v>-2.34</x:v>
+        <x:v>-0.97</x:v>
       </x:c>
       <x:c r="E23" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="F23" s="0">
         <x:v>1.52</x:v>
@@ -940,19 +940,19 @@
         <x:v>28</x:v>
       </x:c>
       <x:c r="B24" s="0">
-        <x:v>19.32</x:v>
+        <x:v>17.07</x:v>
       </x:c>
       <x:c r="C24" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D24" s="0">
-        <x:v>-21.69</x:v>
+        <x:v>-22.57</x:v>
       </x:c>
       <x:c r="E24" s="0">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F24" s="0">
-        <x:v>1.52</x:v>
+        <x:v>1.51</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:6">
@@ -960,16 +960,16 @@
         <x:v>29</x:v>
       </x:c>
       <x:c r="B25" s="0">
-        <x:v>16.25</x:v>
+        <x:v>14.48</x:v>
       </x:c>
       <x:c r="C25" s="0">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D25" s="0">
-        <x:v>-15.18</x:v>
+        <x:v>-16.46</x:v>
       </x:c>
       <x:c r="E25" s="0">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F25" s="0">
         <x:v>1.37</x:v>
@@ -980,16 +980,16 @@
         <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="0">
-        <x:v>18.04</x:v>
+        <x:v>15.41</x:v>
       </x:c>
       <x:c r="C26" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D26" s="0">
-        <x:v>-13.95</x:v>
+        <x:v>-15.86</x:v>
       </x:c>
       <x:c r="E26" s="0">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="F26" s="0">
         <x:v>1.37</x:v>
@@ -1000,16 +1000,16 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="B27" s="0">
-        <x:v>13.04</x:v>
+        <x:v>12.2</x:v>
       </x:c>
       <x:c r="C27" s="0">
-        <x:v>22</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D27" s="0">
-        <x:v>-21.39</x:v>
+        <x:v>-21.98</x:v>
       </x:c>
       <x:c r="E27" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F27" s="0">
         <x:v>1.44</x:v>
@@ -1023,13 +1023,13 @@
         <x:v>13.69</x:v>
       </x:c>
       <x:c r="C28" s="0">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D28" s="0">
         <x:v>-15.88</x:v>
       </x:c>
       <x:c r="E28" s="0">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F28" s="0">
         <x:v>1.35</x:v>
@@ -1040,19 +1040,19 @@
         <x:v>33</x:v>
       </x:c>
       <x:c r="B29" s="0">
-        <x:v>136.76</x:v>
+        <x:v>129.47</x:v>
       </x:c>
       <x:c r="C29" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D29" s="0">
-        <x:v>-1.24</x:v>
+        <x:v>-5.2</x:v>
       </x:c>
       <x:c r="E29" s="0">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="F29" s="0">
-        <x:v>2.4</x:v>
+        <x:v>2.42</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:6">
@@ -1060,7 +1060,7 @@
         <x:v>34</x:v>
       </x:c>
       <x:c r="B30" s="0">
-        <x:v>370.03</x:v>
+        <x:v>389.82</x:v>
       </x:c>
       <x:c r="C30" s="0">
         <x:v>100</x:v>
@@ -1072,7 +1072,7 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="F30" s="0">
-        <x:v>4.7</x:v>
+        <x:v>4.9</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:6">
@@ -1080,16 +1080,16 @@
         <x:v>35</x:v>
       </x:c>
       <x:c r="B31" s="0">
-        <x:v>41.38</x:v>
+        <x:v>37.63</x:v>
       </x:c>
       <x:c r="C31" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>-24.62</x:v>
+        <x:v>-26.62</x:v>
       </x:c>
       <x:c r="E31" s="0">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F31" s="0">
         <x:v>1.88</x:v>
